--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -24614,6 +24614,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1055">
+      <c r="A1055" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1055" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C1055" t="n">
+        <v>0.589999973773956</v>
+      </c>
+      <c r="D1055" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="E1055" t="n">
+        <v>0.569999992847443</v>
+      </c>
+      <c r="F1055" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="G1055" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -24637,6 +24637,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1056">
+      <c r="A1056" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1056" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C1056" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="D1056" t="n">
+        <v>0.535000026226044</v>
+      </c>
+      <c r="E1056" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="F1056" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="G1056" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -24660,6 +24660,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1057">
+      <c r="A1057" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1057" t="n">
+        <v>22500</v>
+      </c>
+      <c r="C1057" t="n">
+        <v>0.555000007152557</v>
+      </c>
+      <c r="D1057" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="E1057" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="F1057" t="n">
+        <v>0.555000007152557</v>
+      </c>
+      <c r="G1057" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -24683,6 +24683,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1058">
+      <c r="A1058" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1058" t="n">
+        <v>11250</v>
+      </c>
+      <c r="C1058" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="D1058" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="E1058" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="F1058" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="G1058" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -24524,22 +24524,22 @@
     </row>
     <row r="1051">
       <c r="A1051" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1051" t="n">
-        <v>51250</v>
+        <v>8750</v>
       </c>
       <c r="C1051" t="n">
-        <v>0.600000023841858</v>
+        <v>0.574999988079071</v>
       </c>
       <c r="D1051" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="E1051" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="F1051" t="n">
         <v>0.574999988079071</v>
-      </c>
-      <c r="E1051" t="n">
-        <v>0.574999988079071</v>
-      </c>
-      <c r="F1051" t="n">
-        <v>0.589999973773956</v>
       </c>
       <c r="G1051" t="s">
         <v>7</v>
@@ -24547,22 +24547,22 @@
     </row>
     <row r="1052">
       <c r="A1052" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1052" t="n">
-        <v>55000</v>
+        <v>51250</v>
       </c>
       <c r="C1052" t="n">
         <v>0.600000023841858</v>
       </c>
       <c r="D1052" t="n">
-        <v>0.555000007152557</v>
+        <v>0.574999988079071</v>
       </c>
       <c r="E1052" t="n">
-        <v>0.595000028610229</v>
+        <v>0.574999988079071</v>
       </c>
       <c r="F1052" t="n">
-        <v>0.579999983310699</v>
+        <v>0.589999973773956</v>
       </c>
       <c r="G1052" t="s">
         <v>7</v>
@@ -24570,22 +24570,22 @@
     </row>
     <row r="1053">
       <c r="A1053" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1053" t="n">
-        <v>12500</v>
+        <v>55000</v>
       </c>
       <c r="C1053" t="n">
-        <v>0.564999997615814</v>
+        <v>0.600000023841858</v>
       </c>
       <c r="D1053" t="n">
-        <v>0.540000021457672</v>
+        <v>0.555000007152557</v>
       </c>
       <c r="E1053" t="n">
-        <v>0.564999997615814</v>
+        <v>0.595000028610229</v>
       </c>
       <c r="F1053" t="n">
-        <v>0.545000016689301</v>
+        <v>0.579999983310699</v>
       </c>
       <c r="G1053" t="s">
         <v>7</v>
@@ -24593,22 +24593,22 @@
     </row>
     <row r="1054">
       <c r="A1054" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1054" t="n">
-        <v>82500</v>
+        <v>12500</v>
       </c>
       <c r="C1054" t="n">
-        <v>0.574999988079071</v>
+        <v>0.564999997615814</v>
       </c>
       <c r="D1054" t="n">
-        <v>0.519999980926514</v>
+        <v>0.540000021457672</v>
       </c>
       <c r="E1054" t="n">
-        <v>0.529999971389771</v>
+        <v>0.564999997615814</v>
       </c>
       <c r="F1054" t="n">
-        <v>0.564999997615814</v>
+        <v>0.545000016689301</v>
       </c>
       <c r="G1054" t="s">
         <v>7</v>
@@ -24616,22 +24616,22 @@
     </row>
     <row r="1055">
       <c r="A1055" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1055" t="n">
-        <v>25000</v>
+        <v>82500</v>
       </c>
       <c r="C1055" t="n">
-        <v>0.589999973773956</v>
+        <v>0.574999988079071</v>
       </c>
       <c r="D1055" t="n">
-        <v>0.540000021457672</v>
+        <v>0.519999980926514</v>
       </c>
       <c r="E1055" t="n">
-        <v>0.569999992847443</v>
+        <v>0.529999971389771</v>
       </c>
       <c r="F1055" t="n">
-        <v>0.545000016689301</v>
+        <v>0.564999997615814</v>
       </c>
       <c r="G1055" t="s">
         <v>7</v>
@@ -24639,22 +24639,22 @@
     </row>
     <row r="1056">
       <c r="A1056" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1056" t="n">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="C1056" t="n">
-        <v>0.550000011920929</v>
+        <v>0.589999973773956</v>
       </c>
       <c r="D1056" t="n">
-        <v>0.535000026226044</v>
+        <v>0.540000021457672</v>
       </c>
       <c r="E1056" t="n">
-        <v>0.550000011920929</v>
+        <v>0.569999992847443</v>
       </c>
       <c r="F1056" t="n">
-        <v>0.540000021457672</v>
+        <v>0.545000016689301</v>
       </c>
       <c r="G1056" t="s">
         <v>7</v>
@@ -24662,22 +24662,22 @@
     </row>
     <row r="1057">
       <c r="A1057" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1057" t="n">
-        <v>22500</v>
+        <v>20000</v>
       </c>
       <c r="C1057" t="n">
-        <v>0.555000007152557</v>
+        <v>0.550000011920929</v>
       </c>
       <c r="D1057" t="n">
-        <v>0.529999971389771</v>
+        <v>0.535000026226044</v>
       </c>
       <c r="E1057" t="n">
-        <v>0.545000016689301</v>
+        <v>0.550000011920929</v>
       </c>
       <c r="F1057" t="n">
-        <v>0.555000007152557</v>
+        <v>0.540000021457672</v>
       </c>
       <c r="G1057" t="s">
         <v>7</v>
@@ -24685,22 +24685,22 @@
     </row>
     <row r="1058">
       <c r="A1058" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1058" t="n">
-        <v>11250</v>
+        <v>22500</v>
       </c>
       <c r="C1058" t="n">
-        <v>0.550000011920929</v>
+        <v>0.555000007152557</v>
       </c>
       <c r="D1058" t="n">
-        <v>0.540000021457672</v>
+        <v>0.529999971389771</v>
       </c>
       <c r="E1058" t="n">
-        <v>0.540000021457672</v>
+        <v>0.545000016689301</v>
       </c>
       <c r="F1058" t="n">
-        <v>0.550000011920929</v>
+        <v>0.555000007152557</v>
       </c>
       <c r="G1058" t="s">
         <v>7</v>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -24706,6 +24706,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1059">
+      <c r="A1059" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1059" t="n">
+        <v>11250</v>
+      </c>
+      <c r="C1059" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="D1059" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="E1059" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="F1059" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="G1059" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1060" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="D1060" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="E1060" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="F1060" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="G1060" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -24752,6 +24752,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1061">
+      <c r="A1061" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1061" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="D1061" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="E1061" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="F1061" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="G1061" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -28013,6 +28013,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1064">
+      <c r="A1064" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1064" t="n">
+        <v>11250</v>
+      </c>
+      <c r="C1064" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="D1064" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="E1064" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="F1064" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="G1064" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="H1064" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -28039,6 +28039,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1065">
+      <c r="A1065" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1065" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C1065" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="D1065" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E1065" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="F1065" t="n">
+        <v>0.493999987840652</v>
+      </c>
+      <c r="G1065" t="n">
+        <v>0.493999987840652</v>
+      </c>
+      <c r="H1065" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -28117,6 +28117,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1068">
+      <c r="A1068" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1068" t="n">
+        <v>63750</v>
+      </c>
+      <c r="C1068" t="n">
+        <v>0.48199999332428</v>
+      </c>
+      <c r="D1068" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="E1068" t="n">
+        <v>0.48199999332428</v>
+      </c>
+      <c r="F1068" t="n">
+        <v>0.48199999332428</v>
+      </c>
+      <c r="G1068" t="n">
+        <v>0.48199999332428</v>
+      </c>
+      <c r="H1068" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -24982,6 +24982,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1071">
+      <c r="A1071" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1071" t="n">
+        <v>0.495999991893768</v>
+      </c>
+      <c r="D1071" t="n">
+        <v>0.495999991893768</v>
+      </c>
+      <c r="E1071" t="n">
+        <v>0.495999991893768</v>
+      </c>
+      <c r="F1071" t="n">
+        <v>0.495999991893768</v>
+      </c>
+      <c r="G1071" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1072" t="n">
+        <v>12500</v>
+      </c>
+      <c r="C1072" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="D1072" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E1072" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1072"/>
+      <c r="G1072" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -25021,8 +25021,31 @@
       <c r="E1072" t="n">
         <v>0.5</v>
       </c>
-      <c r="F1072"/>
+      <c r="F1072" t="n">
+        <v>0.509999990463257</v>
+      </c>
       <c r="G1072" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1073" t="n">
+        <v>6250</v>
+      </c>
+      <c r="C1073" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="D1073" t="n">
+        <v>0.504999995231628</v>
+      </c>
+      <c r="E1073" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="F1073"/>
+      <c r="G1073" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -25044,8 +25044,31 @@
       <c r="E1073" t="n">
         <v>0.514999985694885</v>
       </c>
-      <c r="F1073"/>
+      <c r="F1073" t="n">
+        <v>0.504999995231628</v>
+      </c>
       <c r="G1073" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1074" t="n">
+        <v>16250</v>
+      </c>
+      <c r="C1074" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="D1074" t="n">
+        <v>0.488000005483627</v>
+      </c>
+      <c r="E1074" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="F1074"/>
+      <c r="G1074" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -25067,8 +25067,31 @@
       <c r="E1074" t="n">
         <v>0.490000009536743</v>
       </c>
-      <c r="F1074"/>
+      <c r="F1074" t="n">
+        <v>0.490000009536743</v>
+      </c>
       <c r="G1074" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1075" t="n">
+        <v>23750</v>
+      </c>
+      <c r="C1075" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="D1075" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="E1075" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="F1075"/>
+      <c r="G1075" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -25097,6 +25097,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1076">
+      <c r="A1076" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1076" t="n">
+        <v>93750</v>
+      </c>
+      <c r="C1076" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="D1076" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E1076" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="F1076" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="G1076" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -28403,6 +28403,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1079">
+      <c r="A1079" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1079" t="n">
+        <v>743750</v>
+      </c>
+      <c r="C1079" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="D1079" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="E1079" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="F1079" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="G1079" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="H1079" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -28429,6 +28429,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1080">
+      <c r="A1080" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1080" t="n">
+        <v>571250</v>
+      </c>
+      <c r="C1080" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="D1080" t="n">
+        <v>0.492000013589859</v>
+      </c>
+      <c r="E1080" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="F1080" t="n">
+        <v>0.493999987840652</v>
+      </c>
+      <c r="G1080" t="n">
+        <v>0.493999987840652</v>
+      </c>
+      <c r="H1080" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -31698,6 +31698,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1081">
+      <c r="A1081" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1081" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1081" t="n">
+        <v>0.493999987840652</v>
+      </c>
+      <c r="D1081" t="n">
+        <v>0.493999987840652</v>
+      </c>
+      <c r="E1081" t="n">
+        <v>0.465999990701675</v>
+      </c>
+      <c r="F1081" t="n">
+        <v>0.474000006914139</v>
+      </c>
+      <c r="G1081" t="n">
+        <v>0.474000006914139</v>
+      </c>
+      <c r="H1081" t="n">
+        <v>171250</v>
+      </c>
+      <c r="I1081" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1082" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1082" t="n">
+        <v>0.467999994754791</v>
+      </c>
+      <c r="D1082" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="E1082" t="n">
+        <v>0.44200000166893</v>
+      </c>
+      <c r="F1082" t="n">
+        <v>0.458000004291534</v>
+      </c>
+      <c r="G1082" t="n">
+        <v>0.458000004291534</v>
+      </c>
+      <c r="H1082" t="n">
+        <v>127500</v>
+      </c>
+      <c r="I1082" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -31750,9 +31750,38 @@
         <v>0.458000004291534</v>
       </c>
       <c r="H1082" t="n">
-        <v>127500</v>
+        <v>125000</v>
       </c>
       <c r="I1082" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1083" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1083" t="n">
+        <v>0.449999988079071</v>
+      </c>
+      <c r="D1083" t="n">
+        <v>0.449999988079071</v>
+      </c>
+      <c r="E1083" t="n">
+        <v>0.40599998831749</v>
+      </c>
+      <c r="F1083" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="G1083" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="H1083" t="n">
+        <v>180000</v>
+      </c>
+      <c r="I1083" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -31779,9 +31779,38 @@
         <v>0.419999986886978</v>
       </c>
       <c r="H1083" t="n">
-        <v>180000</v>
+        <v>182500</v>
       </c>
       <c r="I1083" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1084" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1084" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="D1084" t="n">
+        <v>0.435999989509583</v>
+      </c>
+      <c r="E1084" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="F1084" t="n">
+        <v>0.432000011205673</v>
+      </c>
+      <c r="G1084" t="n">
+        <v>0.432000011205673</v>
+      </c>
+      <c r="H1084" t="n">
+        <v>103750</v>
+      </c>
+      <c r="I1084" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -31814,6 +31814,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1085">
+      <c r="A1085" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1085" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1085" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="D1085" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="E1085" t="n">
+        <v>0.40200001001358</v>
+      </c>
+      <c r="F1085" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="G1085" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="H1085" t="n">
+        <v>71250</v>
+      </c>
+      <c r="I1085" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -31843,6 +31843,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1086">
+      <c r="A1086" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1086" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1086" t="n">
+        <v>0.428000003099442</v>
+      </c>
+      <c r="D1086" t="n">
+        <v>0.428000003099442</v>
+      </c>
+      <c r="E1086" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="F1086" t="n">
+        <v>0.418000012636185</v>
+      </c>
+      <c r="G1086" t="n">
+        <v>0.418000012636185</v>
+      </c>
+      <c r="H1086" t="n">
+        <v>28750</v>
+      </c>
+      <c r="I1086" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -31872,6 +31872,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1087">
+      <c r="A1087" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1087" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1087" t="n">
+        <v>0.42399999499321</v>
+      </c>
+      <c r="D1087" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1087" t="n">
+        <v>0.42399999499321</v>
+      </c>
+      <c r="F1087" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="G1087" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="H1087" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I1087" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -31901,6 +31901,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1088">
+      <c r="A1088" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1088" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1088" t="n">
+        <v>0.446000009775162</v>
+      </c>
+      <c r="D1088" t="n">
+        <v>0.458000004291534</v>
+      </c>
+      <c r="E1088" t="n">
+        <v>0.425999999046326</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>0.449999988079071</v>
+      </c>
+      <c r="G1088" t="n">
+        <v>0.449999988079071</v>
+      </c>
+      <c r="H1088" t="n">
+        <v>126250</v>
+      </c>
+      <c r="I1088" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -31930,6 +31930,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1089">
+      <c r="A1089" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1089" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1089" t="n">
+        <v>0.458000004291534</v>
+      </c>
+      <c r="D1089" t="n">
+        <v>0.462000012397766</v>
+      </c>
+      <c r="E1089" t="n">
+        <v>0.451999992132187</v>
+      </c>
+      <c r="F1089" t="n">
+        <v>0.462000012397766</v>
+      </c>
+      <c r="G1089" t="n">
+        <v>0.462000012397766</v>
+      </c>
+      <c r="H1089" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I1089" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POZ.MI.xlsx
+++ b/data/POZ.MI.xlsx
@@ -31959,6 +31959,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1090">
+      <c r="A1090" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1090" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1090" t="n">
+        <v>0.465999990701675</v>
+      </c>
+      <c r="D1090" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="E1090" t="n">
+        <v>0.456000000238419</v>
+      </c>
+      <c r="F1090" t="n">
+        <v>0.477999985218048</v>
+      </c>
+      <c r="G1090" t="n">
+        <v>0.477999985218048</v>
+      </c>
+      <c r="H1090" t="n">
+        <v>208750</v>
+      </c>
+      <c r="I1090" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
